--- a/nmoreau/ig/ValueSet-consent-information-status.xlsx
+++ b/nmoreau/ig/ValueSet-consent-information-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-05T08:51:40+00:00</t>
+    <t>2025-05-06T13:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
